--- a/Result/checksun_type/風場開發.xlsx
+++ b/Result/checksun_type/風場開發.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>41.23</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>46.87</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>46.87</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>31333478.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>46398517.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>46398517.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>131458358.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>82367727.08</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>82367727.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-12563936.95104639</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>31333478</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>31333478.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>41.15</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>45.63</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>46.99</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>45.63</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>46.99</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>36693061.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>56607545.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>56607545.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>134181709.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>82624485.32</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>82624485.31999999</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-9404152.255840585</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>36693061</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>36693061.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>40.98999999999999</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>45.99</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>47.13</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>45.99</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>47.13</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>52683153.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>89118941.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>89118941.40000001</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>138816628.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>83437284.84</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>83437284.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-5128552.57498084</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>52683153</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>52683153.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>41.09</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>46.37</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>47.28</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>46.37</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>47.28</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>45580107.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>111884228.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>111884228.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>138885693.6</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>83731647.22</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>83731647.22</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-550614.5817890316</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>45580107</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>45580107.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>41.45</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>46.82</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>47.42</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>47.42</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>65702790.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>146516831.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>146516831</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>138891629.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>86052402.7</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>86052402.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>6770002.28640601</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>65702790</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>65702790.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>42.15</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>47.27</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>47.55</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>47.27</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>47.55</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>82378616.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>216518198.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>216518198.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>143652333.4</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>85485799.7</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>85485799.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>14830238.83788446</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>82378616</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>82378616.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>43.67</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>47.72</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>47.67</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>47.72</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>47.67</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>199250041.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>211755874.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>211755874.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>140443251.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>84907732.44</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>84907732.44</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>24028515.4529292</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>199250041</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>199250041.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>45.36</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>48.22</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>47.82</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>47.82</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>166509589.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>188514316.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>188514316.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>128881598.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>82208595.36</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>82208595.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>23788810.95824565</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>166509589</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>166509589.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>46.89</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>48.6</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>47.92</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>47.92</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>218743119.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>165887158.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>165887158.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>115754398.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>79329370.94</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>79329370.94</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>26104681.14590324</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>218743119</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>218743119.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>48.22000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>48.9</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>48</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>415709627.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>131266427.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>131266427.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>98323015.2</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>75737222.34</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>75737222.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>22884307.44448899</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>415709627</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>415709627.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>49.17999999999999</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>48.04</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>48.04</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>58566995.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>70786468.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>70786468.40000001</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>61990972.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>67919282.7</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>67919282.7</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-3637077.537691697</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>58566995</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>58566995.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>94.82000000000001</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>110.55</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>120.29</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>110.55</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>120.29</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>85372388.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>87185433.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>87185433</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>100908050.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>135612783.8</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>135612783.8</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-10806196.54681982</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>85372388</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>85372388.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>94.24</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>112.08</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>120.96</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>112.08</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>120.96</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>40156204.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>80920719.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>80920719.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>115753005.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>140922183.74</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>140922183.74</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-11588934.76875174</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>40156204</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>40156204.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>95.16</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>113.74</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>121.85</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>113.74</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>121.85</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>72611586.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>95067077.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>95067077.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>125497148.7</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>143167309.18</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>143167309.18</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-7448650.55834192</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>72611586</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>72611586.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>96.78</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>115.27</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>122.69</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>115.27</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>122.69</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>146799516.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>103253918.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>103253918.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>130081910.2</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>144056654.78</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>144056654.78</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-4745297.952101409</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>146799516</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>146799516.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>98.86</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>116.94</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>123.59</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>116.94</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>123.59</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>90987471.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>97652026.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>97652026.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>122532657.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>144997711.74</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>144997711.74</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-8662597.516325638</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>90987471</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>90987471.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>100.58</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>118.52</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>124.52</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>118.52</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>124.52</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>54048822.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>114630667.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>114630667.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>116860703.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>144760389.02</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>144760389.02</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-7969499.303920045</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>54048822</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>54048822.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>103.08</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>120.02</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>125.42</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>120.02</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>125.42</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>110887994.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>150585291.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>150585291.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>118001869.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>147490993.98</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>147490993.98</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-2737021.632486328</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>110887994</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>110887994.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>106.9</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>121.6</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>126.28</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>126.28</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>113545789.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>155927219.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>155927219.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>113918881.1</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>148451857.52</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>148451857.52</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-1254214.043563634</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>113545789</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>113545789.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>111.1</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>123.22</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>127.19</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>123.22</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>127.19</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>118790058.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>156909902.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>156909902</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>111648899.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>149115440.26</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>149115440.26</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>624112.1207388937</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>118790058</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>118790058.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>115.4</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>125.05</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>128.1</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>125.05</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>128.1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>175880674.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>147413287.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>147413287.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>115816386.9</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>150786648.46</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>150786648.46</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>2723259.529716134</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>175880674</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>175880674.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>119.7</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>126.75</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>129.01</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>129.01</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>233821943.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>119090740.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>119090740.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>111168830.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>157686513.68</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>157686513.68</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-492069.4406634271</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>233821943</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>233821943.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>94.72</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>103.4</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>113.16</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>113.16</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>95847231.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>90614477.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>90614477.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>138889380.7</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>105041075.58</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>105041075.58</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-6827071.798233047</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>95847231</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>95847231.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>94.16</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>104.56</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>113.72</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>104.56</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>113.72</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>67321456.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>94038150.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>94038150.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>157712250.0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>106002417.36</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>106002417.36</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-5886756.587254092</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>67321456</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>67321456.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>94.52</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>105.75</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>114.43</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>114.43</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>80963156.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>120488195.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>120488195.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>163355703.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>106523920.48</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>106523920.48</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-1276874.80059652</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>80963156</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>80963156.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>94.85999999999999</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>107.04</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>115.12</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>107.04</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>115.12</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>109398449.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>148499153.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>148499153</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>172034039.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>105942739.22</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>105942739.22</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>3892662.566078454</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>109398449</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>109398449.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>94.3</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>108.38</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>115.78</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>108.38</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>115.78</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>99542097.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>164947483.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>164947483.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>169196001.4</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>104900333.08</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>104900333.08</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>8092053.74825421</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>99542097</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>99542097.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>94.58</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>109.82</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>116.48</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>109.82</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>116.48</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>112965593.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>187164283.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>187164283.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>167467742.8</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>104281257.74</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>104281257.74</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>14858219.80321047</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>112965593</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>112965593.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>95.4</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>111.22</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>117.21</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>111.22</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>117.21</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>199571684.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>221386349.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>221386349.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>162838452.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>105235000.58</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>105235000.58</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>22555288.88874766</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>199571684</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>199571684.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>96.67999999999999</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>112.64</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>117.79</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>112.64</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>117.79</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>221017942.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>206223211.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>206223211.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>151025437.1</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>102233227.78</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>102233227.78</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>23466331.8006312</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>221017942</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>221017942.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>98.97999999999999</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>114.04</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>118.42</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>114.04</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>118.42</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>191640102.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>195568925.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>195568925.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>137026694.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>99428759.42</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>99428759.42</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>21631925.03901371</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>191640102</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>191640102.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>102.84</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>115.66</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>119.08</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>115.66</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>119.08</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>210626097.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>173444519.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>173444519.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>124609231.6</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>98146156.82</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>98146156.81999999</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>21386400.91388111</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>210626097</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>210626097.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>106.5</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>117.0</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>119.74</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>117</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>119.74</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>284075924.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>147771202.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>147771202</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>108516997.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>96164726.12</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>96164726.12</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>18237638.38105305</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>284075924</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>284075924.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>39.01000000000001</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>48.62</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>54.24</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>54.24</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>83358150.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>103153046.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>103153046</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>0</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-3680363.644825548</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>83358150</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>83358150.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>38.81</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>49.61</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>54.55</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>54.55</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>70285205.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>116746722.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>116746722.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>0</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-252677.836492613</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>70285205</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>70285205.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>39.4</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>50.62</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>54.92</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>54.92</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>82791269.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>201446352.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>201446352.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>0</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>6053713.06242919</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>82791269</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>82791269.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>39.73</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>51.71</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>55.28</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>55.28</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>154811716.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>200122209.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>200122209.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>0</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>13506703.45151642</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>154811716</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>154811716.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>40.59</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>52.74</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>55.61</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>52.74</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>55.61</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>124518890.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>178692409.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>178692409.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>0</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>15954973.84837258</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>124518890</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>124518890.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>42.70999999999999</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>53.86</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>55.96</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>53.86</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>55.96</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>151326532.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>0</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>0</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>22128342.42072523</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>151326532</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>151326532.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>44.64</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>54.97</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>56.3</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>56.3</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>493783356.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>0</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>0</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>27284895.0804888</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>493783356</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>493783356.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>46.5</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>55.96</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>56.57</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>56.57</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>76170552.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>0</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>0</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-3014864.229866385</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>76170552</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>76170552.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>49.34</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>57.02</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>56.89</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>57.02</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>56.89</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>47662718.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>0</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>0</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-1448331.950735688</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>47662718</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>47662718.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>51.77999999999999</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>57.86</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>57.1</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>57.86</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>57.1</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>0</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>0</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>6046878.730569392</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>0</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>53.46</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>58.38</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>57.23</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>58.38</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>57.23</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>173211166.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>113037476.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>113037476.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>103615588.0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>97097036.24</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>97097036.23999999</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>6046878.730569392</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>173211166</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>173211166.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>31.12</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>33.95</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>33.95</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>17391925.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>24945827.4</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>24945827.4</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>0</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-5187307.558847457</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>17391925</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>17391925.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>25.66</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>31.63</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>34.09</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>34.09</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>14123190.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>34052459.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>34052459.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>0</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-3643777.178724259</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>14123190</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>14123190.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>25.69</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>32.18</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>34.27</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>34.27</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>16265843.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>80665488.6</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>80665488.59999999</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>0</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-958377.2721652538</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>16265843</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>16265843.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>26.03</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>32.79</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>34.46</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>34.46</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>35607113.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>84219876.2</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>84219876.2</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>0</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>2682566.104067795</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>35607113</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>35607113.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>26.98</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>33.41</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>34.66</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>34.66</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>41341066.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>81947035.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>81947035.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>0</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>5715828.923541166</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>41341066</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>41341066.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>28.61</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>34.05</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>34.84</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>34.84</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>62925085.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>0</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>0</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>9230572.66837664</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>62925085</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>62925085.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>30.1</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>34.69</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>35.02</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>34.69</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>35.02</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>247188336.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>0</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>0</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>11609398.38712816</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>247188336</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>247188336.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>31.47</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>35.38</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>35.18</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>35.38</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>35.18</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>34037781.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>0</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>0</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-5149391.707052823</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>34037781</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>34037781.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>32.81</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>35.96</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>35.33</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>35.96</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>35.33</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>24242908.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>0</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>0</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-6069054.102059469</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>24242908</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>24242908.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>33.60000000000001</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>36.37</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>35.42</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>36.37</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>35.42</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>0</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>0</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-5918603.298963025</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>0</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>33.82</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>36.63</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>35.47</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>35.47</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>14998956.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>34520283.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>34520283.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>32085998.6</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>45710534.7</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>45710534.7</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-5918603.298963025</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>14998956</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>14998956.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>17.25</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>18.16</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>13613928.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>10372257.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>10372257.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>15735161.0</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>35709154.84</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>35709154.84</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-2546499.088265551</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>13613928</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>13613928.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>17.08</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>18.26</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>20.36</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>20.36</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>8481553.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>10158688.6</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>10158688.6</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>15635933.7</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>36006631.54</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>36006631.54</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-2868767.912395775</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>8481553</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>8481553.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>17.13</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>18.41</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>20.43</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>20.43</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>11267596.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>15708299.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>15708299.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>16935768.7</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>36089158.58</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>36089158.58</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-2676798.628567677</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>11267596</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>11267596.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>17.24</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>18.57</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>20.5</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>13526868.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>15807963.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>15807963.6</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>17674597.8</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>36309850.68</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>36309850.68</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-2605461.450650116</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>13526868</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>13526868.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>17.44</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>18.77</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>20.58</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>20.58</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>4971344.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>18192489.6</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>18192489.6</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>17817474.1</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>36286025.3</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>36286025.3</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-2652563.858958956</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>4971344</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>4971344.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>17.64</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>20.66</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>20.66</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>12546082.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>21098064.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>21098064.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>19015490.5</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>36438805.22</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>36438805.22</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-1708455.304437336</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>12546082</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>12546082.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>17.93</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>19.27</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>20.75</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>20.75</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>36229606.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>21113178.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>21113178.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>19952648.9</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>36367077.28</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>36367077.28</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-1110291.608533688</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>36229606</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>36229606.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>18.08</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>19.51</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>20.83</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>20.83</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>11765918.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>18163238.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>18163238.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>18465394.1</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>35922851.76</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>35922851.76</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-2753639.199795127</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>11765918</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>11765918.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>18.21</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>20.91</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>20.91</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>25449498.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>19541232.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>19541232</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>19684784.3</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>35922462.82</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>35922462.82</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-2381824.930175934</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>25449498</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>25449498.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>18.34</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>21</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>19499217.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>17442458.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>17442458.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>18972660.0</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>35662849.28</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>35662849.28</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-3231694.368927941</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>19499217</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>19499217.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>18.42</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>20.21</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>21.07</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>20.21</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>21.07</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>12621655.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>16932916.8</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>16932916.8</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>19086589.9</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>35528913.86</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>35528913.86</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-3692845.803969096</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>12621655</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>12621655.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>37.84</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>36.94</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>36.93</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>36.93</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>120416322.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>280072163.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>280072163</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>277426832.9</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>200154771.9</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>200154771.9</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>14388099.54638198</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>120416322</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>120416322.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>37.76000000000001</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>36.85</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>36.89</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>36.85</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>36.89</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>206096332.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>311473909.8</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>311473909.8</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>275431895.7</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>202581225.0</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>202581225</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>31383448.08971417</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>206096332</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>206096332.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>37.62</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>36.78</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>36.86</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>36.78</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>36.86</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>651269647.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>352300593.6</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>352300593.6</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>266468929.3</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>202369157.08</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>202369157.08</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>45361678.93412757</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>651269647</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>651269647.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>37.48</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>36.72</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>36.82</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>36.82</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>218965347.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>285520921.8</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>285520921.8</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>227340167.8</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>193138591.86</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>193138591.86</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>16013379.28564209</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>218965347</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>218965347.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>37.48</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>36.73</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>36.8</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>36.73</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>36.8</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>203613167.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>281712122.2</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>281712122.2</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>217589197.5</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>191062131.4</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>191062131.4</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>19833648.38474703</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>203613167</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>203613167.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>37.4</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>36.72</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>36.78</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>36.78</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>277425056.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>274781502.8</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>274781502.8</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>209108494.5</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>189889393.8</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>189889393.8</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>26227707.51258457</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>277425056</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>277425056.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>37.27</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>36.69</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>36.75</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>36.75</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>410229751.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>239389881.6</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>239389881.6</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>193854808.3</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>186839318.84</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>186839318.84</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>26516957.17690307</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>410229751</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>410229751.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>37.21999999999999</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>36.67</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>36.74</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>36.74</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>317371288.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>180637265.0</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>180637265</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>167115803.0</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>181158923.66</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>181158923.66</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>11754062.33389726</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>317371288</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>317371288.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>37.14</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>36.63</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>36.71</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>36.71</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>199921349.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>169159413.8</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>169159413.8</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>165563914.9</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>177543829.44</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>177543829.44</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>193545.6533926129</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>199921349</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>199921349.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>36.88</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>36.58</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>36.69</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>36.58</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>36.69</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>168960070.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>153466272.8</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>153466272.8</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>157164946.8</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>177846992.98</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>177846992.98</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-3744468.484949499</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>168960070</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>168960070.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>36.63</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>36.56</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>36.69</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>36.56</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>36.69</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>100466950.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>143435486.2</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>143435486.2</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>163956437.7</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>180812768.7</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>180812768.7</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-5919192.058118582</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>100466950</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>100466950.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
